--- a/WorkBot/refactor/data/orders/Hillcrest Dairy/Hillcrest Dairy_Collegetown_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/Hillcrest Dairy/Hillcrest Dairy_Collegetown_2025-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,33 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>skimg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Milk - Skim</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15.56</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31.12</t>
         </is>
       </c>
     </row>
